--- a/output/pdf_financials_xlsx/TRAC.xlsx
+++ b/output/pdf_financials_xlsx/TRAC.xlsx
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>2.011702</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.950301</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.950301</v>
       </c>
     </row>
     <row r="93">
@@ -3071,7 +3071,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
         <v>2.011702</v>
       </c>

--- a/output/pdf_financials_xlsx/TRAC.xlsx
+++ b/output/pdf_financials_xlsx/TRAC.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.861425</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.722647</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.466636</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.861425</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.722647</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.466636</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.082493</v>
+        <v>0.221068</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.736189</v>
+        <v>0.013542</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.479836</v>
+        <v>0.0132</v>
       </c>
     </row>
     <row r="49">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
